--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486983_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486983_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.853</v>
+        <v>6.2557</v>
       </c>
       <c r="E2" t="n">
-        <v>5.6123</v>
+        <v>7.1039</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.7593</v>
+        <v>-0.8482</v>
       </c>
       <c r="G2" t="n">
         <v>5.9661</v>
@@ -610,13 +610,13 @@
         <v>1.4374</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.0433</v>
+        <v>0.3593</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.6782</v>
+        <v>0.8133</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.3651</v>
+        <v>-0.454</v>
       </c>
       <c r="V2" t="n">
         <v>-0.4805</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.8193</v>
+        <v>1.1628</v>
       </c>
       <c r="E3" t="n">
-        <v>6.4939</v>
+        <v>4.3631</v>
       </c>
       <c r="F3" t="n">
-        <v>-3.6746</v>
+        <v>-3.2003</v>
       </c>
       <c r="G3" t="n">
         <v>3.0127</v>
@@ -688,13 +688,13 @@
         <v>1.2321</v>
       </c>
       <c r="S3" t="n">
-        <v>3.2255</v>
+        <v>1.569</v>
       </c>
       <c r="T3" t="n">
-        <v>4.5326</v>
+        <v>2.4018</v>
       </c>
       <c r="U3" t="n">
-        <v>-1.307</v>
+        <v>-0.8328</v>
       </c>
       <c r="V3" t="n">
         <v>-2.5975</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.4811</v>
+        <v>-0.7604</v>
       </c>
       <c r="E4" t="n">
-        <v>2.9481</v>
+        <v>2.4909</v>
       </c>
       <c r="F4" t="n">
-        <v>-3.4292</v>
+        <v>-3.2513</v>
       </c>
       <c r="G4" t="n">
         <v>0.9712</v>
@@ -766,13 +766,13 @@
         <v>0.8214</v>
       </c>
       <c r="S4" t="n">
-        <v>0.08359999999999999</v>
+        <v>-0.1957</v>
       </c>
       <c r="T4" t="n">
-        <v>0.4725</v>
+        <v>0.0154</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.3889</v>
+        <v>-0.211</v>
       </c>
       <c r="V4" t="n">
         <v>-2.3573</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>O. BRAMBLE</t>
+          <t>J. HIERREZUELO SERER</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.8021</v>
+        <v>-1.4501</v>
       </c>
       <c r="E5" t="n">
-        <v>1.349</v>
+        <v>-1.8446</v>
       </c>
       <c r="F5" t="n">
-        <v>-2.1511</v>
+        <v>0.3945</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.8813</v>
+        <v>-0.3805</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.4184</v>
+        <v>0.2693</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.4629</v>
+        <v>-0.6498</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.4214</v>
+        <v>-1.294</v>
       </c>
       <c r="K5" t="n">
-        <v>0.2759</v>
+        <v>0.1007</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.6974</v>
+        <v>-1.3947</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.4599</v>
+        <v>0.9134</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.6943</v>
+        <v>0.1686</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.7655999999999999</v>
+        <v>0.7449</v>
       </c>
       <c r="P5" t="n">
-        <v>0.616</v>
+        <v>-0.4107</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-1.0267</v>
       </c>
       <c r="R5" t="n">
         <v>0.616</v>
       </c>
       <c r="S5" t="n">
-        <v>1.6418</v>
+        <v>0.6286</v>
       </c>
       <c r="T5" t="n">
-        <v>1.7704</v>
+        <v>0.5849</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.1286</v>
+        <v>0.0437</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.1786</v>
+        <v>-1.2875</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>-0.1088</v>
       </c>
       <c r="X5" t="n">
         <v>-1.1786</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. HIERREZUELO SERER</t>
+          <t>O. BRAMBLE</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,64 +877,64 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.6428</v>
+        <v>-2.012</v>
       </c>
       <c r="E6" t="n">
-        <v>-2.1855</v>
+        <v>0.1984</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5427</v>
+        <v>-2.2104</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.3805</v>
+        <v>-1.8813</v>
       </c>
       <c r="H6" t="n">
-        <v>0.2693</v>
+        <v>-0.4184</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.6498</v>
+        <v>-1.4629</v>
       </c>
       <c r="J6" t="n">
-        <v>-1.294</v>
+        <v>-0.4214</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1007</v>
+        <v>0.2759</v>
       </c>
       <c r="L6" t="n">
-        <v>-1.3947</v>
+        <v>-0.6974</v>
       </c>
       <c r="M6" t="n">
-        <v>0.9134</v>
+        <v>-1.4599</v>
       </c>
       <c r="N6" t="n">
-        <v>0.1686</v>
+        <v>-0.6943</v>
       </c>
       <c r="O6" t="n">
-        <v>0.7449</v>
+        <v>-0.7655999999999999</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.4107</v>
+        <v>0.616</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.0267</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
         <v>0.616</v>
       </c>
       <c r="S6" t="n">
-        <v>0.4359</v>
+        <v>0.4319</v>
       </c>
       <c r="T6" t="n">
-        <v>0.244</v>
+        <v>0.6198</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1919</v>
+        <v>-0.1879</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.2875</v>
+        <v>-1.1786</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.1088</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
         <v>-1.1786</v>
@@ -955,10 +955,10 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.3698</v>
+        <v>-2.2652</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.0863</v>
+        <v>-0.9817</v>
       </c>
       <c r="F7" t="n">
         <v>-1.2835</v>
@@ -1000,10 +1000,10 @@
         <v>0.8214</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.4766</v>
+        <v>-0.372</v>
       </c>
       <c r="T7" t="n">
-        <v>0.0309</v>
+        <v>0.1355</v>
       </c>
       <c r="U7" t="n">
         <v>-0.5075</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-3.0904</v>
+        <v>-3.1793</v>
       </c>
       <c r="E8" t="n">
         <v>-1.4875</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.6029</v>
+        <v>-1.6918</v>
       </c>
       <c r="G8" t="n">
         <v>-0.9374</v>
@@ -1078,13 +1078,13 @@
         <v>0.2053</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.0011</v>
+        <v>-0.0901</v>
       </c>
       <c r="T8" t="n">
         <v>-0.1317</v>
       </c>
       <c r="U8" t="n">
-        <v>0.1306</v>
+        <v>0.0417</v>
       </c>
       <c r="V8" t="n">
         <v>-2.3573</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-4.1382</v>
+        <v>-3.1819</v>
       </c>
       <c r="E9" t="n">
-        <v>-4.1463</v>
+        <v>-2.864</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0081</v>
+        <v>-0.3179</v>
       </c>
       <c r="G9" t="n">
         <v>-3.8543</v>
@@ -1156,13 +1156,13 @@
         <v>1.4374</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.5427</v>
+        <v>0.4136</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.4883</v>
+        <v>0.794</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.0543</v>
+        <v>-0.3804</v>
       </c>
       <c r="V9" t="n">
         <v>-1.1786</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-5.9545</v>
+        <v>-5.3063</v>
       </c>
       <c r="E10" t="n">
-        <v>-5.4001</v>
+        <v>-4.8112</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.5544</v>
+        <v>-0.4951</v>
       </c>
       <c r="G10" t="n">
         <v>-5.1656</v>
@@ -1234,13 +1234,13 @@
         <v>1.0267</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.7005</v>
+        <v>-0.0524</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.5115</v>
+        <v>0.0774</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.189</v>
+        <v>-0.1297</v>
       </c>
       <c r="V10" t="n">
         <v>0.9384</v>
@@ -1267,10 +1267,10 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-9.955</v>
+        <v>-9.366099999999999</v>
       </c>
       <c r="E11" t="n">
-        <v>-6.5538</v>
+        <v>-5.965</v>
       </c>
       <c r="F11" t="n">
         <v>-3.4011</v>
@@ -1312,10 +1312,10 @@
         <v>1.0267</v>
       </c>
       <c r="S11" t="n">
-        <v>0.2053</v>
+        <v>0.7942</v>
       </c>
       <c r="T11" t="n">
-        <v>0.8405</v>
+        <v>1.4294</v>
       </c>
       <c r="U11" t="n">
         <v>-0.6351</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-20.7616</v>
+        <v>-20.1028</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.456199999999998</v>
+        <v>-3.797699999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>-16.3053</v>
+        <v>-16.3051</v>
       </c>
       <c r="G12" t="n">
         <v>-10.1871</v>
@@ -1366,7 +1366,7 @@
         <v>-2.300899999999999</v>
       </c>
       <c r="K12" t="n">
-        <v>6.883300000000002</v>
+        <v>6.8833</v>
       </c>
       <c r="L12" t="n">
         <v>-9.1845</v>
@@ -1375,7 +1375,7 @@
         <v>-7.8864</v>
       </c>
       <c r="N12" t="n">
-        <v>-4.429799999999999</v>
+        <v>-4.4298</v>
       </c>
       <c r="O12" t="n">
         <v>-3.456299999999999</v>
@@ -1390,10 +1390,10 @@
         <v>9.240399999999999</v>
       </c>
       <c r="S12" t="n">
-        <v>2.827899999999999</v>
+        <v>3.4864</v>
       </c>
       <c r="T12" t="n">
-        <v>6.081200000000001</v>
+        <v>6.739800000000001</v>
       </c>
       <c r="U12" t="n">
         <v>-3.253</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>D. KANDULU</t>
+          <t>A. MEANA PEREZ</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>9.911</v>
+        <v>9.307600000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>8.7628</v>
+        <v>7.8498</v>
       </c>
       <c r="F13" t="n">
-        <v>1.1481</v>
+        <v>1.4578</v>
       </c>
       <c r="G13" t="n">
-        <v>4.6211</v>
+        <v>4.6978</v>
       </c>
       <c r="H13" t="n">
-        <v>3.3896</v>
+        <v>0.8071</v>
       </c>
       <c r="I13" t="n">
-        <v>1.2315</v>
+        <v>3.8907</v>
       </c>
       <c r="J13" t="n">
-        <v>3.9408</v>
+        <v>4.0489</v>
       </c>
       <c r="K13" t="n">
-        <v>3.5462</v>
+        <v>1.5767</v>
       </c>
       <c r="L13" t="n">
-        <v>0.3947</v>
+        <v>2.4722</v>
       </c>
       <c r="M13" t="n">
-        <v>0.6803</v>
+        <v>0.6488</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.1566</v>
+        <v>-0.7696</v>
       </c>
       <c r="O13" t="n">
-        <v>0.8368</v>
+        <v>1.4185</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>-1.2321</v>
       </c>
       <c r="Q13" t="n">
-        <v>-1.2321</v>
+        <v>-2.0534</v>
       </c>
       <c r="R13" t="n">
-        <v>1.2321</v>
+        <v>0.8214</v>
       </c>
       <c r="S13" t="n">
-        <v>2.3433</v>
+        <v>-0.2915</v>
       </c>
       <c r="T13" t="n">
-        <v>2.2779</v>
+        <v>-0.2791</v>
       </c>
       <c r="U13" t="n">
-        <v>0.0654</v>
+        <v>-0.0124</v>
       </c>
       <c r="V13" t="n">
-        <v>2.9466</v>
+        <v>6.1334</v>
       </c>
       <c r="W13" t="n">
-        <v>3.7761</v>
+        <v>6.1334</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.8295</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A. MEANA PEREZ</t>
+          <t>D. KANDULU</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>7.7367</v>
+        <v>9.0671</v>
       </c>
       <c r="E14" t="n">
-        <v>7.2222</v>
+        <v>7.7168</v>
       </c>
       <c r="F14" t="n">
-        <v>0.5145999999999999</v>
+        <v>1.3503</v>
       </c>
       <c r="G14" t="n">
-        <v>4.6978</v>
+        <v>4.6211</v>
       </c>
       <c r="H14" t="n">
-        <v>0.8071</v>
+        <v>3.3896</v>
       </c>
       <c r="I14" t="n">
-        <v>3.8907</v>
+        <v>1.2315</v>
       </c>
       <c r="J14" t="n">
-        <v>4.0489</v>
+        <v>3.9408</v>
       </c>
       <c r="K14" t="n">
-        <v>1.5767</v>
+        <v>3.5462</v>
       </c>
       <c r="L14" t="n">
-        <v>2.4722</v>
+        <v>0.3947</v>
       </c>
       <c r="M14" t="n">
-        <v>0.6488</v>
+        <v>0.6803</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.7696</v>
+        <v>-0.1566</v>
       </c>
       <c r="O14" t="n">
-        <v>1.4185</v>
+        <v>0.8368</v>
       </c>
       <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
         <v>-1.2321</v>
       </c>
-      <c r="Q14" t="n">
-        <v>-2.0534</v>
-      </c>
       <c r="R14" t="n">
-        <v>0.8214</v>
+        <v>1.2321</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.8624</v>
+        <v>1.4994</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.9068000000000001</v>
+        <v>1.2319</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.9556</v>
+        <v>0.2675</v>
       </c>
       <c r="V14" t="n">
-        <v>6.1334</v>
+        <v>2.9466</v>
       </c>
       <c r="W14" t="n">
-        <v>6.1334</v>
+        <v>3.7761</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>-0.8295</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.2734</v>
+        <v>2.4128</v>
       </c>
       <c r="E15" t="n">
         <v>1.3018</v>
       </c>
       <c r="F15" t="n">
-        <v>0.9715</v>
+        <v>1.111</v>
       </c>
       <c r="G15" t="n">
         <v>2.7808</v>
@@ -1624,13 +1624,13 @@
         <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.5075</v>
+        <v>-0.368</v>
       </c>
       <c r="T15" t="n">
         <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.5075</v>
+        <v>-0.368</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>M. ENABULELE OGUNSUYI</t>
+          <t>D. RIVAS PALMER</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.3662</v>
+        <v>2.0042</v>
       </c>
       <c r="E16" t="n">
-        <v>1.5459</v>
+        <v>0.2053</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.1798</v>
+        <v>1.7989</v>
       </c>
       <c r="G16" t="n">
-        <v>1.3252</v>
+        <v>0.7945</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.6036</v>
+        <v>-1.1232</v>
       </c>
       <c r="I16" t="n">
-        <v>1.9288</v>
+        <v>1.9177</v>
       </c>
       <c r="J16" t="n">
-        <v>1.2633</v>
+        <v>-0.1363</v>
       </c>
       <c r="K16" t="n">
-        <v>0.474</v>
+        <v>-0.6355</v>
       </c>
       <c r="L16" t="n">
-        <v>0.7893</v>
+        <v>0.4993</v>
       </c>
       <c r="M16" t="n">
-        <v>0.0619</v>
+        <v>0.9308</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.0777</v>
+        <v>-0.4877</v>
       </c>
       <c r="O16" t="n">
-        <v>1.1395</v>
+        <v>1.4185</v>
       </c>
       <c r="P16" t="n">
-        <v>0.2053</v>
+        <v>0.616</v>
       </c>
       <c r="Q16" t="n">
         <v>-1.0267</v>
       </c>
       <c r="R16" t="n">
-        <v>1.2321</v>
+        <v>1.6427</v>
       </c>
       <c r="S16" t="n">
-        <v>0.0759</v>
+        <v>-0.585</v>
       </c>
       <c r="T16" t="n">
-        <v>1.3093</v>
+        <v>0.1896</v>
       </c>
       <c r="U16" t="n">
-        <v>-1.2334</v>
+        <v>-0.7746</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.2402</v>
+        <v>1.1786</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.1786</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.2402</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.0856</v>
+        <v>1.6836</v>
       </c>
       <c r="E17" t="n">
-        <v>0.6579</v>
+        <v>0.8671</v>
       </c>
       <c r="F17" t="n">
-        <v>0.4277</v>
+        <v>0.8165</v>
       </c>
       <c r="G17" t="n">
         <v>0.7489</v>
@@ -1780,13 +1780,13 @@
         <v>1.4374</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.1355</v>
+        <v>-0.5375</v>
       </c>
       <c r="T17" t="n">
-        <v>0.1858</v>
+        <v>0.395</v>
       </c>
       <c r="U17" t="n">
-        <v>-1.3214</v>
+        <v>-0.9326</v>
       </c>
       <c r="V17" t="n">
         <v>0.2402</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>D. RIVAS PALMER</t>
+          <t>A. RIVAS PALMER</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.5258</v>
+        <v>1.4619</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.3177</v>
+        <v>-0.406</v>
       </c>
       <c r="F18" t="n">
-        <v>0.8435</v>
+        <v>1.868</v>
       </c>
       <c r="G18" t="n">
-        <v>0.7945</v>
+        <v>-0.0692</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.1232</v>
+        <v>-2.2291</v>
       </c>
       <c r="I18" t="n">
-        <v>1.9177</v>
+        <v>2.1599</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.1363</v>
+        <v>-0.4997</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.6355</v>
+        <v>-0.9859</v>
       </c>
       <c r="L18" t="n">
-        <v>0.4993</v>
+        <v>0.4863</v>
       </c>
       <c r="M18" t="n">
-        <v>0.9308</v>
+        <v>0.4304</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.4877</v>
+        <v>-1.2432</v>
       </c>
       <c r="O18" t="n">
-        <v>1.4185</v>
+        <v>1.6736</v>
       </c>
       <c r="P18" t="n">
-        <v>0.616</v>
+        <v>-0</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.0267</v>
+        <v>-2.0534</v>
       </c>
       <c r="R18" t="n">
-        <v>1.6427</v>
+        <v>2.0534</v>
       </c>
       <c r="S18" t="n">
-        <v>-2.0634</v>
+        <v>0.1123</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.3334</v>
+        <v>0.2477</v>
       </c>
       <c r="U18" t="n">
-        <v>-1.73</v>
+        <v>-0.1354</v>
       </c>
       <c r="V18" t="n">
-        <v>1.1786</v>
+        <v>1.4189</v>
       </c>
       <c r="W18" t="n">
-        <v>1.1786</v>
+        <v>1.8993</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-0.4805</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. RIVAS PALMER</t>
+          <t>M. ENABULELE OGUNSUYI</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.5205</v>
+        <v>0.6723</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.929</v>
+        <v>0.3953</v>
       </c>
       <c r="F19" t="n">
-        <v>1.4496</v>
+        <v>0.277</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.0692</v>
+        <v>1.3252</v>
       </c>
       <c r="H19" t="n">
-        <v>-2.2291</v>
+        <v>-0.6036</v>
       </c>
       <c r="I19" t="n">
-        <v>2.1599</v>
+        <v>1.9288</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.4997</v>
+        <v>1.2633</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.9859</v>
+        <v>0.474</v>
       </c>
       <c r="L19" t="n">
-        <v>0.4863</v>
+        <v>0.7893</v>
       </c>
       <c r="M19" t="n">
-        <v>0.4304</v>
+        <v>0.0619</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.2432</v>
+        <v>-1.0777</v>
       </c>
       <c r="O19" t="n">
-        <v>1.6736</v>
+        <v>1.1395</v>
       </c>
       <c r="P19" t="n">
-        <v>-0</v>
+        <v>0.2053</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.0534</v>
+        <v>-1.0267</v>
       </c>
       <c r="R19" t="n">
-        <v>2.0534</v>
+        <v>1.2321</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.8290999999999999</v>
+        <v>-0.618</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.2753</v>
+        <v>0.1587</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.5538</v>
+        <v>-0.7766</v>
       </c>
       <c r="V19" t="n">
-        <v>1.4189</v>
+        <v>-0.2402</v>
       </c>
       <c r="W19" t="n">
-        <v>1.8993</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.4805</v>
+        <v>-0.2402</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.1076</v>
+        <v>-0.0658</v>
       </c>
       <c r="E20" t="n">
         <v>-0.0143</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.09329999999999999</v>
+        <v>-0.0515</v>
       </c>
       <c r="G20" t="n">
         <v>0.035</v>
@@ -2014,13 +2014,13 @@
         <v>0.8214</v>
       </c>
       <c r="S20" t="n">
-        <v>0.5084</v>
+        <v>0.5502</v>
       </c>
       <c r="T20" t="n">
         <v>0.3757</v>
       </c>
       <c r="U20" t="n">
-        <v>0.1326</v>
+        <v>0.1744</v>
       </c>
       <c r="V20" t="n">
         <v>-0.2402</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.3288</v>
+        <v>-0.4578</v>
       </c>
       <c r="E21" t="n">
-        <v>0.1551</v>
+        <v>-0.0541</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.4839</v>
+        <v>-0.4037</v>
       </c>
       <c r="G21" t="n">
         <v>-0.6728</v>
@@ -2092,13 +2092,13 @@
         <v>0.4107</v>
       </c>
       <c r="S21" t="n">
-        <v>0.3789</v>
+        <v>0.2499</v>
       </c>
       <c r="T21" t="n">
-        <v>0.368</v>
+        <v>0.1588</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0109</v>
+        <v>0.0911</v>
       </c>
       <c r="V21" t="n">
         <v>-0.2402</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.2213</v>
+        <v>-1.1404</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.0794</v>
+        <v>-1.5564</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.1418</v>
+        <v>0.4161</v>
       </c>
       <c r="G22" t="n">
         <v>-4.0741</v>
@@ -2170,13 +2170,13 @@
         <v>0.616</v>
       </c>
       <c r="S22" t="n">
-        <v>0.2635</v>
+        <v>1.3444</v>
       </c>
       <c r="T22" t="n">
-        <v>0.2517</v>
+        <v>0.7747000000000001</v>
       </c>
       <c r="U22" t="n">
-        <v>0.0118</v>
+        <v>0.5697</v>
       </c>
       <c r="V22" t="n">
         <v>1.1786</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>20.7615</v>
+        <v>24.9455</v>
       </c>
       <c r="E23" t="n">
         <v>16.3053</v>
       </c>
       <c r="F23" t="n">
-        <v>4.4562</v>
+        <v>8.6404</v>
       </c>
       <c r="G23" t="n">
         <v>10.1872</v>
@@ -2221,7 +2221,7 @@
         <v>12.6406</v>
       </c>
       <c r="J23" t="n">
-        <v>7.886100000000001</v>
+        <v>7.886099999999999</v>
       </c>
       <c r="K23" t="n">
         <v>4.43</v>
@@ -2248,13 +2248,13 @@
         <v>10.2672</v>
       </c>
       <c r="S23" t="n">
-        <v>-2.8279</v>
+        <v>1.3562</v>
       </c>
       <c r="T23" t="n">
-        <v>3.252899999999999</v>
+        <v>3.253</v>
       </c>
       <c r="U23" t="n">
-        <v>-6.081</v>
+        <v>-1.8969</v>
       </c>
       <c r="V23" t="n">
         <v>12.3757</v>
